--- a/InputData/fuels/FSPbPPT/Fuel Surcharge Perc by Power Plant Type.xlsx
+++ b/InputData/fuels/FSPbPPT/Fuel Surcharge Perc by Power Plant Type.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\fuels\FSPbPPT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-india\InputData\fuels\FSPbPPT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65263F8A-FDBA-4D8E-81F2-4CDEE15290AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C904C880-3688-4DE5-BF9C-9DC5ED2AD397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="730" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="FSPbPPT" sheetId="17" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,6 +28,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,15 +39,63 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
+    <t>FSPbPPT Fuel Surcharge Percentage by Power Plant Type</t>
+  </si>
+  <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Generally, costs of fuels for the electricity sector should be specified in BFPaT BAU Fuel Prices and Taxes.</t>
+  </si>
+  <si>
+    <t>However, that variable is subscripted by All Fuels, not by Electricity Source (i.e., power plant type).</t>
+  </si>
+  <si>
+    <t>Peaking power plants, which only consume small amounts of fuel at irregular intervals, may face higher costs</t>
+  </si>
+  <si>
+    <t>per unit fuel than a power plant that purchases larger quantities of fuel at a steady rate.</t>
+  </si>
+  <si>
+    <t>Therefore, it is necessary to apply a surcharge to plant types that use the same fuel type as other plants</t>
+  </si>
+  <si>
+    <t>but pay higher prices per unit of fuel purchased than those other plants.</t>
+  </si>
+  <si>
+    <t>This mostly applies to natural gas peaker plants and natural gas steam turbines, which buy the same fuel as</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle plants, but face higher costs per unit fuel than natural gas combined cycle plants.</t>
+  </si>
+  <si>
+    <t>Unit: dimensionless (percentage)</t>
+  </si>
+  <si>
+    <t>Fuel Surcharge Percentage</t>
+  </si>
+  <si>
+    <t>hard coal</t>
+  </si>
+  <si>
+    <t>natural gas steam turbine</t>
+  </si>
+  <si>
+    <t>natural gas combined cycle</t>
+  </si>
+  <si>
     <t>nuclear</t>
   </si>
   <si>
     <t>hydro</t>
   </si>
   <si>
+    <t>onshore wind</t>
+  </si>
+  <si>
     <t>solar PV</t>
   </si>
   <si>
@@ -64,21 +114,12 @@
     <t>natural gas peaker</t>
   </si>
   <si>
-    <t>Notes</t>
-  </si>
-  <si>
     <t>lignite</t>
   </si>
   <si>
     <t>offshore wind</t>
   </si>
   <si>
-    <t>onshore wind</t>
-  </si>
-  <si>
-    <t>hard coal</t>
-  </si>
-  <si>
     <t>crude oil</t>
   </si>
   <si>
@@ -86,45 +127,6 @@
   </si>
   <si>
     <t>municipal solid waste</t>
-  </si>
-  <si>
-    <t>natural gas steam turbine</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle</t>
-  </si>
-  <si>
-    <t>Unit: dimensionless (percentage)</t>
-  </si>
-  <si>
-    <t>Fuel Surcharge Percentage</t>
-  </si>
-  <si>
-    <t>FSPbPPT Fuel Surcharge Percentage by Power Plant Type</t>
-  </si>
-  <si>
-    <t>Generally, costs of fuels for the electricity sector should be specified in BFPaT BAU Fuel Prices and Taxes.</t>
-  </si>
-  <si>
-    <t>However, that variable is subscripted by All Fuels, not by Electricity Source (i.e., power plant type).</t>
-  </si>
-  <si>
-    <t>Peaking power plants, which only consume small amounts of fuel at irregular intervals, may face higher costs</t>
-  </si>
-  <si>
-    <t>per unit fuel than a power plant that purchases larger quantities of fuel at a steady rate.</t>
-  </si>
-  <si>
-    <t>but pay higher prices per unit of fuel purchased than those other plants.</t>
-  </si>
-  <si>
-    <t>This mostly applies to natural gas peaker plants and natural gas steam turbines, which buy the same fuel as</t>
-  </si>
-  <si>
-    <t>natural gas combined cycle plants, but face higher costs per unit fuel than natural gas combined cycle plants.</t>
-  </si>
-  <si>
-    <t>Therefore, it is necessary to apply a surcharge to plant types that use the same fuel type as other plants</t>
   </si>
   <si>
     <t>hard coal w CCS</t>
@@ -152,7 +154,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -202,13 +204,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -239,7 +234,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -254,9 +249,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -548,12 +540,12 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="4"/>
     </row>
@@ -565,47 +557,47 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -628,10 +620,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -644,15 +636,15 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -660,7 +652,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -668,7 +660,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -676,7 +668,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -684,7 +676,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -692,7 +684,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -700,7 +692,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -708,7 +700,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -716,7 +708,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -724,15 +716,15 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B13">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -740,7 +732,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -748,7 +740,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -756,7 +748,7 @@
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -764,7 +756,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -811,7 +803,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24" s="7">
@@ -819,7 +811,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+      <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25" s="7">
@@ -830,4 +822,198 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="77cd1fc208aa16a525090c2a27f33c66">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d77402130d0e9b5bbfbb66ed18db98d9" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2FBCCC7-4FBE-454B-9655-A562706AAD03}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{988780B6-2FE4-4D4C-A5A1-21B74072D4CF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A32FC201-E3F4-407F-9114-D3895BC6E383}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>